--- a/owlcms/src/main/resources/templates/start/NestedStartListByPlatform.xlsx
+++ b/owlcms/src/main/resources/templates/start/NestedStartListByPlatform.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\local\templates\start\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\start\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7FA9078-8EC0-4EEE-9DBA-6E890862AAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C2657F-431B-441E-B777-DD9021AC454B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>jx:each(
   items="platforms"
@@ -490,45 +490,18 @@
     <t>${competition.competitionName}</t>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Session</t>
-  </si>
-  <si>
     <t>${agi.ageGroup.code}</t>
   </si>
   <si>
     <t>${session.name}</t>
   </si>
   <si>
-    <t>Age</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Cat</t>
-  </si>
-  <si>
-    <t>Lot</t>
-  </si>
-  <si>
     <t>${athlete.age}</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>${athlete.entryTotal}</t>
   </si>
   <si>
-    <t>Team</t>
-  </si>
-  <si>
     <t>${session.athletes.0.ageGroup.gender}</t>
   </si>
   <si>
@@ -536,9 +509,6 @@
   </si>
   <si>
     <t>${athlete.lotNumber}</t>
-  </si>
-  <si>
-    <t>Gndr</t>
   </si>
   <si>
     <t>${athlete.ageGroupCodesAsString}</t>
@@ -568,7 +538,37 @@
     <t>${platform.name}</t>
   </si>
   <si>
-    <t>Competitions</t>
+    <t>${t.get("Group")}</t>
+  </si>
+  <si>
+    <t>${t.get("Competition.competitionDate")}</t>
+  </si>
+  <si>
+    <t>${t.get("Gender")}</t>
+  </si>
+  <si>
+    <t>${t.get("AgeGoup")}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.Category")}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.Lot")}</t>
+  </si>
+  <si>
+    <t>${t.get("Age")}</t>
+  </si>
+  <si>
+    <t>${t.get("Name")}</t>
+  </si>
+  <si>
+    <t>${t.get("EntryTotal")}</t>
+  </si>
+  <si>
+    <t>${t.get("Team")}</t>
+  </si>
+  <si>
+    <t>${t.get("Competitions")}</t>
   </si>
 </sst>
 </file>
@@ -628,7 +628,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -674,7 +674,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -694,30 +694,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1066,69 +1065,69 @@
     <col min="6" max="7" width="5.85546875" customWidth="1"/>
     <col min="8" max="8" width="28.85546875" customWidth="1"/>
     <col min="9" max="9" width="5.85546875" customWidth="1"/>
-    <col min="10" max="10" width="16.42578125" style="15" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" style="11" customWidth="1"/>
     <col min="11" max="11" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
     </row>
-    <row r="2" spans="1:11" s="12" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:11" s="8" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="9"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="13"/>
-    </row>
-    <row r="3" spans="1:11" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>23</v>
@@ -1136,37 +1135,37 @@
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>20</v>
+      <c r="J4" s="10" t="s">
+        <v>10</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/owlcms/src/main/resources/templates/start/NestedStartListByPlatform.xlsx
+++ b/owlcms/src/main/resources/templates/start/NestedStartListByPlatform.xlsx
@@ -50,7 +50,9 @@
             <rFont val="Aptos Narrow"/>
             <family val="2"/>
           </rPr>
-          <t>jx:area(lastCell="K4")</t>
+          <t>jx:area(lastCell="K4")
+owlcms:horizontalBorders(4, 1, 5)
+owlcms:verticalBorders(4, 1, 11)</t>
         </r>
       </text>
     </comment>
